--- a/resources/templates/Checklist_Positions/Template_HT1.xlsx
+++ b/resources/templates/Checklist_Positions/Template_HT1.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="118">
   <si>
     <t>Checklist For Action in the Regional/Field Office</t>
   </si>
@@ -1029,7 +1029,7 @@
     <t>Recommended:</t>
   </si>
   <si>
-    <t>KIANNE CAILA R. ABAT</t>
+    <t>${encoder_name}</t>
   </si>
   <si>
     <t>RONALD KEVIN C. DEL ROSARIO</t>
@@ -1038,7 +1038,7 @@
     <t>VERNA C. CABAYA</t>
   </si>
   <si>
-    <t>Administrative Aide I</t>
+    <t>${user_position}</t>
   </si>
   <si>
     <t>Administrative Officer IV-HR</t>
@@ -1047,10 +1047,7 @@
     <t>Administrative Officer V</t>
   </si>
   <si>
-    <t>Date: June 23, 2025</t>
-  </si>
-  <si>
-    <t>Date:  June 23, 2025</t>
+    <t>Date: ${date_of_signing}</t>
   </si>
   <si>
     <t>APC Form - (Revised 2018)</t>
@@ -5598,7 +5595,7 @@
       </c>
       <c r="B86" s="235"/>
       <c r="C86" s="236" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D86" s="237" t="s">
         <v>116</v>
@@ -5611,7 +5608,7 @@
     </row>
     <row r="87" s="2" customFormat="1" ht="12.75" customHeight="1" spans="1:10">
       <c r="A87" s="240" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B87" s="241"/>
     </row>
